--- a/MetalCutter Kit - MPX PrintNC V4 BOM - Enriched.xlsx
+++ b/MetalCutter Kit - MPX PrintNC V4 BOM - Enriched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\printnc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\model\Documents\Github\printnc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F2B14C4-7A85-4847-BAEE-37402211FCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E2A2F1-6CE3-4972-B924-47110AD21D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B4231DBA-BBEA-4181-96C9-90C830E52136}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4231DBA-BBEA-4181-96C9-90C830E52136}"/>
   </bookViews>
   <sheets>
     <sheet name="MetalCutter Kit - MPX PrintNC V" sheetId="1" r:id="rId1"/>
@@ -1487,7 +1487,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1618,6 +1618,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1920,7 +1928,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1963,11 +1971,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -2001,6 +2011,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -2342,9 +2353,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC14D861-C44D-42B7-BC7F-4F1B44F819EF}">
   <dimension ref="A1:K113"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="11" width="20.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2387,7 +2401,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2395,12 +2409,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2408,7 +2422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2416,7 +2430,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2424,7 +2438,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2449,11 +2463,11 @@
       <c r="J12" t="s">
         <v>23</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -2475,11 +2489,11 @@
       <c r="J13" t="s">
         <v>29</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>30</v>
       </c>
@@ -2505,7 +2519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -2527,11 +2541,11 @@
       <c r="J15" t="s">
         <v>39</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>41</v>
       </c>
@@ -2553,11 +2567,11 @@
       <c r="J16" t="s">
         <v>45</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>46</v>
       </c>
@@ -2579,11 +2593,11 @@
       <c r="J17" t="s">
         <v>39</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>50</v>
       </c>
@@ -2605,11 +2619,11 @@
       <c r="J18" t="s">
         <v>29</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>54</v>
       </c>
@@ -2631,11 +2645,11 @@
       <c r="J19" t="s">
         <v>29</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>58</v>
       </c>
@@ -2657,11 +2671,11 @@
       <c r="J20" t="s">
         <v>62</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>64</v>
       </c>
@@ -2686,11 +2700,11 @@
       <c r="J21" t="s">
         <v>70</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>72</v>
       </c>
@@ -2715,11 +2729,11 @@
       <c r="J22" t="s">
         <v>74</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>75</v>
       </c>
@@ -2741,11 +2755,11 @@
       <c r="J23" t="s">
         <v>80</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>82</v>
       </c>
@@ -2767,11 +2781,11 @@
       <c r="J24" t="s">
         <v>84</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>85</v>
       </c>
@@ -2793,11 +2807,11 @@
       <c r="J25" t="s">
         <v>29</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>89</v>
       </c>
@@ -2819,11 +2833,11 @@
       <c r="J26" t="s">
         <v>94</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>95</v>
       </c>
@@ -2858,7 +2872,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>104</v>
       </c>
@@ -2890,7 +2904,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>107</v>
       </c>
@@ -2922,7 +2936,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>113</v>
       </c>
@@ -2951,7 +2965,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>117</v>
       </c>
@@ -2980,7 +2994,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -3012,7 +3026,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>127</v>
       </c>
@@ -3038,7 +3052,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>133</v>
       </c>
@@ -3067,7 +3081,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>136</v>
       </c>
@@ -3093,7 +3107,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>138</v>
       </c>
@@ -3122,7 +3136,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>145</v>
       </c>
@@ -3148,7 +3162,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>151</v>
       </c>
@@ -3180,7 +3194,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>158</v>
       </c>
@@ -3209,7 +3223,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>160</v>
       </c>
@@ -3238,7 +3252,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>166</v>
       </c>
@@ -3264,7 +3278,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>171</v>
       </c>
@@ -3293,7 +3307,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>179</v>
       </c>
@@ -3319,7 +3333,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>185</v>
       </c>
@@ -3345,7 +3359,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>187</v>
       </c>
@@ -3374,7 +3388,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>190</v>
       </c>
@@ -3400,7 +3414,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>193</v>
       </c>
@@ -3426,7 +3440,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>199</v>
       </c>
@@ -3452,7 +3466,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>206</v>
       </c>
@@ -3481,7 +3495,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>213</v>
       </c>
@@ -3510,7 +3524,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>213</v>
       </c>
@@ -3539,7 +3553,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>221</v>
       </c>
@@ -3568,7 +3582,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>229</v>
       </c>
@@ -3600,7 +3614,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>237</v>
       </c>
@@ -3626,7 +3640,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>244</v>
       </c>
@@ -3655,7 +3669,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>252</v>
       </c>
@@ -3678,7 +3692,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>256</v>
       </c>
@@ -3701,7 +3715,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>258</v>
       </c>
@@ -3724,7 +3738,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>260</v>
       </c>
@@ -3747,7 +3761,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>263</v>
       </c>
@@ -3770,7 +3784,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>266</v>
       </c>
@@ -3793,7 +3807,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>268</v>
       </c>
@@ -3816,7 +3830,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>270</v>
       </c>
@@ -3839,7 +3853,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>272</v>
       </c>
@@ -3862,7 +3876,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>274</v>
       </c>
@@ -3891,7 +3905,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>282</v>
       </c>
@@ -3920,7 +3934,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>283</v>
       </c>
@@ -3946,7 +3960,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>294</v>
       </c>
@@ -3972,7 +3986,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>301</v>
       </c>
@@ -3998,7 +4012,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>308</v>
       </c>
@@ -4024,7 +4038,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>315</v>
       </c>
@@ -4050,7 +4064,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>321</v>
       </c>
@@ -4076,7 +4090,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>328</v>
       </c>
@@ -4102,7 +4116,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>335</v>
       </c>
@@ -4128,7 +4142,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>335</v>
       </c>
@@ -4154,7 +4168,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>346</v>
       </c>
@@ -4183,7 +4197,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>354</v>
       </c>
@@ -4212,7 +4226,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>362</v>
       </c>
@@ -4238,7 +4252,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>368</v>
       </c>
@@ -4264,7 +4278,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>375</v>
       </c>
@@ -4290,7 +4304,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>375</v>
       </c>
@@ -4316,7 +4330,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>375</v>
       </c>
@@ -4342,7 +4356,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>392</v>
       </c>
@@ -4368,7 +4382,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>398</v>
       </c>
@@ -4394,7 +4408,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>404</v>
       </c>
@@ -4426,7 +4440,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>413</v>
       </c>
@@ -4452,7 +4466,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>420</v>
       </c>
@@ -4478,7 +4492,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>427</v>
       </c>
@@ -4507,12 +4521,12 @@
         <v>432</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>434</v>
       </c>
@@ -4541,7 +4555,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>442</v>
       </c>
@@ -4564,7 +4578,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>446</v>
       </c>
@@ -4590,7 +4604,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>452</v>
       </c>
@@ -4610,7 +4624,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>454</v>
       </c>
@@ -4636,7 +4650,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>458</v>
       </c>
@@ -4656,7 +4670,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>460</v>
       </c>
@@ -4679,7 +4693,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>463</v>
       </c>
@@ -4702,7 +4716,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>466</v>
       </c>
@@ -4728,7 +4742,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>470</v>
       </c>
@@ -4751,7 +4765,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>476</v>
       </c>
@@ -4783,7 +4797,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>477</v>
       </c>
@@ -4812,12 +4826,28 @@
         <v>243</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>486</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K12" r:id="rId1" xr:uid="{01F8AA81-6450-4E45-9A29-D449BF8355D1}"/>
+    <hyperlink ref="K13" r:id="rId2" xr:uid="{2BB46EC5-FC56-4365-A123-06EF67E6AD06}"/>
+    <hyperlink ref="K15" r:id="rId3" xr:uid="{A037ED52-9CB7-4466-9AD7-4ADC8CBCF8C2}"/>
+    <hyperlink ref="K16" r:id="rId4" xr:uid="{CB3AC7D3-9462-43CF-9923-320BD3292E5F}"/>
+    <hyperlink ref="K17" r:id="rId5" xr:uid="{F03C1B62-5FDD-45A3-885A-3970EB98EEF8}"/>
+    <hyperlink ref="K18" r:id="rId6" xr:uid="{3F5DF0E5-AA65-4BAA-9582-AE1B3E22757D}"/>
+    <hyperlink ref="K19" r:id="rId7" xr:uid="{C9400FBB-3165-48F7-9DCB-5DB3908C7899}"/>
+    <hyperlink ref="K20" r:id="rId8" xr:uid="{29AA53E0-05D8-4E51-A77C-59FCF3D08A6E}"/>
+    <hyperlink ref="K21" r:id="rId9" xr:uid="{BBB4D8C0-BA2B-4E52-8151-08D2F913C427}"/>
+    <hyperlink ref="K22" r:id="rId10" xr:uid="{A22B5542-ADCF-4F90-A539-7503CE284B21}"/>
+    <hyperlink ref="K23" r:id="rId11" xr:uid="{6B69FCAA-5607-4950-BB20-255F80A60C43}"/>
+    <hyperlink ref="K24" r:id="rId12" xr:uid="{AF717CC2-8D6B-4111-8C20-7ABDCA4DBA8F}"/>
+    <hyperlink ref="K25" r:id="rId13" xr:uid="{AC1CE4E9-7D38-4A12-AA06-E302E016B087}"/>
+    <hyperlink ref="K26" r:id="rId14" xr:uid="{FEC6DC7F-08EA-4777-9F61-05151F4C1272}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>